--- a/productos.xlsx
+++ b/productos.xlsx
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>77.95</v>
+        <v>89.95</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>77.95</v>
+        <v>89.95</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         </is>
       </c>
       <c r="E538" t="n">
-        <v>19.35</v>
+        <v>22.95</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         </is>
       </c>
       <c r="E559" t="n">
-        <v>29.95</v>
+        <v>32.5</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         </is>
       </c>
       <c r="E562" t="n">
-        <v>33.5</v>
+        <v>42.5</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         </is>
       </c>
       <c r="E563" t="n">
-        <v>54.5</v>
+        <v>59.95</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -50272,7 +50272,7 @@
         </is>
       </c>
       <c r="E1059" t="n">
-        <v>19.95</v>
+        <v>20.95</v>
       </c>
       <c r="F1059" t="inlineStr">
         <is>
@@ -50319,7 +50319,7 @@
         </is>
       </c>
       <c r="E1060" t="n">
-        <v>19.5</v>
+        <v>19.95</v>
       </c>
       <c r="F1060" t="inlineStr">
         <is>
@@ -62697,7 +62697,7 @@
         </is>
       </c>
       <c r="E1320" t="n">
-        <v>46.95</v>
+        <v>51.95</v>
       </c>
       <c r="F1320" t="inlineStr">
         <is>
@@ -62744,7 +62744,7 @@
         </is>
       </c>
       <c r="E1321" t="n">
-        <v>86.5</v>
+        <v>90.95</v>
       </c>
       <c r="F1321" t="inlineStr">
         <is>
@@ -63477,7 +63477,7 @@
         </is>
       </c>
       <c r="E1336" t="n">
-        <v>104.95</v>
+        <v>114.95</v>
       </c>
       <c r="F1336" t="inlineStr">
         <is>
@@ -63524,7 +63524,7 @@
         </is>
       </c>
       <c r="E1337" t="n">
-        <v>71.5</v>
+        <v>74.95</v>
       </c>
       <c r="F1337" t="inlineStr">
         <is>
@@ -63571,7 +63571,7 @@
         </is>
       </c>
       <c r="E1338" t="n">
-        <v>85.95</v>
+        <v>94.95</v>
       </c>
       <c r="F1338" t="inlineStr">
         <is>
@@ -63618,7 +63618,7 @@
         </is>
       </c>
       <c r="E1339" t="n">
-        <v>73.5</v>
+        <v>81.95</v>
       </c>
       <c r="F1339" t="inlineStr">
         <is>
@@ -64131,7 +64131,7 @@
         </is>
       </c>
       <c r="E1350" t="n">
-        <v>66.95</v>
+        <v>73.5</v>
       </c>
       <c r="F1350" t="inlineStr">
         <is>
@@ -83392,7 +83392,7 @@
         </is>
       </c>
       <c r="E1761" t="n">
-        <v>34.95</v>
+        <v>41.95</v>
       </c>
       <c r="F1761" t="inlineStr">
         <is>
@@ -86079,7 +86079,7 @@
         </is>
       </c>
       <c r="E1818" t="n">
-        <v>24.95</v>
+        <v>28.5</v>
       </c>
       <c r="F1818" t="inlineStr">
         <is>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1356</v>
+        <v>1356000</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>

--- a/productos.xlsx
+++ b/productos.xlsx
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>59.95</v>
+        <v>53.95</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>59.95</v>
+        <v>53.5</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>65.95</v>
+        <v>59.95</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>63.95</v>
+        <v>58.95</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>65.95</v>
+        <v>60.5</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -24392,7 +24392,7 @@
         </is>
       </c>
       <c r="E509" t="n">
-        <v>28.5</v>
+        <v>25.5</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         </is>
       </c>
       <c r="E755" t="n">
-        <v>70.95</v>
+        <v>74.95</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         </is>
       </c>
       <c r="E756" t="n">
-        <v>36.5</v>
+        <v>38.5</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         </is>
       </c>
       <c r="E757" t="n">
-        <v>34.5</v>
+        <v>36.95</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         </is>
       </c>
       <c r="E758" t="n">
-        <v>66.95</v>
+        <v>71.5</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -36489,7 +36489,7 @@
         </is>
       </c>
       <c r="E766" t="n">
-        <v>86.95</v>
+        <v>95.5</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         </is>
       </c>
       <c r="E767" t="n">
-        <v>82.95</v>
+        <v>89.95</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         </is>
       </c>
       <c r="E768" t="n">
-        <v>59.95</v>
+        <v>76.5</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         </is>
       </c>
       <c r="E769" t="n">
-        <v>63.95</v>
+        <v>80.95</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         </is>
       </c>
       <c r="E770" t="n">
-        <v>85.95</v>
+        <v>88.95</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         </is>
       </c>
       <c r="E771" t="n">
-        <v>80.5</v>
+        <v>83.95</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         </is>
       </c>
       <c r="E772" t="n">
-        <v>80.5</v>
+        <v>85.95</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         </is>
       </c>
       <c r="E781" t="n">
-        <v>98.95</v>
+        <v>99.95</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         </is>
       </c>
       <c r="E782" t="n">
-        <v>142.95</v>
+        <v>146.5</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -38753,7 +38753,7 @@
         </is>
       </c>
       <c r="E814" t="n">
-        <v>43.5</v>
+        <v>41.5</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -40825,7 +40825,7 @@
         </is>
       </c>
       <c r="E858" t="n">
-        <v>29.95</v>
+        <v>28.5</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         </is>
       </c>
       <c r="E861" t="n">
-        <v>43.95</v>
+        <v>36.95</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -47593,7 +47593,7 @@
         </is>
       </c>
       <c r="E1002" t="n">
-        <v>23.95</v>
+        <v>27.95</v>
       </c>
       <c r="F1002" t="inlineStr">
         <is>
@@ -52958,7 +52958,7 @@
         </is>
       </c>
       <c r="E1115" t="n">
-        <v>16.95</v>
+        <v>15.95</v>
       </c>
       <c r="F1115" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         </is>
       </c>
       <c r="E1116" t="n">
-        <v>16.95</v>
+        <v>15.95</v>
       </c>
       <c r="F1116" t="inlineStr">
         <is>
@@ -53311,7 +53311,7 @@
         </is>
       </c>
       <c r="E1122" t="n">
-        <v>40.5</v>
+        <v>38.5</v>
       </c>
       <c r="F1122" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         </is>
       </c>
       <c r="E1123" t="n">
-        <v>40.5</v>
+        <v>38.5</v>
       </c>
       <c r="F1123" t="inlineStr">
         <is>
@@ -53405,7 +53405,7 @@
         </is>
       </c>
       <c r="E1124" t="n">
-        <v>16.95</v>
+        <v>15.95</v>
       </c>
       <c r="F1124" t="inlineStr">
         <is>
@@ -53452,7 +53452,7 @@
         </is>
       </c>
       <c r="E1125" t="n">
-        <v>16.95</v>
+        <v>15.95</v>
       </c>
       <c r="F1125" t="inlineStr">
         <is>
@@ -53499,7 +53499,7 @@
         </is>
       </c>
       <c r="E1126" t="n">
-        <v>16.95</v>
+        <v>15.95</v>
       </c>
       <c r="F1126" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         </is>
       </c>
       <c r="E1127" t="n">
-        <v>16.95</v>
+        <v>15.95</v>
       </c>
       <c r="F1127" t="inlineStr">
         <is>
@@ -53593,7 +53593,7 @@
         </is>
       </c>
       <c r="E1128" t="n">
-        <v>40.5</v>
+        <v>38.5</v>
       </c>
       <c r="F1128" t="inlineStr">
         <is>
@@ -57578,7 +57578,7 @@
         </is>
       </c>
       <c r="E1211" t="n">
-        <v>41.5</v>
+        <v>45.5</v>
       </c>
       <c r="F1211" t="inlineStr">
         <is>
@@ -57672,7 +57672,7 @@
         </is>
       </c>
       <c r="E1213" t="n">
-        <v>41.5</v>
+        <v>45.5</v>
       </c>
       <c r="F1213" t="inlineStr">
         <is>
@@ -60024,7 +60024,7 @@
         </is>
       </c>
       <c r="E1263" t="n">
-        <v>99.95</v>
+        <v>106.95</v>
       </c>
       <c r="F1263" t="inlineStr">
         <is>
@@ -60071,7 +60071,7 @@
         </is>
       </c>
       <c r="E1264" t="n">
-        <v>33.5</v>
+        <v>35.95</v>
       </c>
       <c r="F1264" t="inlineStr">
         <is>
@@ -61287,7 +61287,7 @@
         </is>
       </c>
       <c r="E1290" t="n">
-        <v>24.95</v>
+        <v>22.65</v>
       </c>
       <c r="F1290" t="inlineStr">
         <is>
@@ -61380,7 +61380,9 @@
           <t>6.76 OZ</t>
         </is>
       </c>
-      <c r="E1292" t="inlineStr"/>
+      <c r="E1292" t="n">
+        <v>22.5</v>
+      </c>
       <c r="F1292" t="inlineStr">
         <is>
           <t>INCAPARINA TETRAPACK</t>
@@ -67915,7 +67917,7 @@
         </is>
       </c>
       <c r="E1430" t="n">
-        <v>106.95</v>
+        <v>94.95</v>
       </c>
       <c r="F1430" t="inlineStr">
         <is>
@@ -67966,7 +67968,7 @@
         </is>
       </c>
       <c r="E1431" t="n">
-        <v>105.95</v>
+        <v>84.95</v>
       </c>
       <c r="F1431" t="inlineStr">
         <is>
@@ -70978,7 +70980,7 @@
         </is>
       </c>
       <c r="E1497" t="n">
-        <v>288.5</v>
+        <v>255.95</v>
       </c>
       <c r="F1497" t="inlineStr">
         <is>
@@ -71025,7 +71027,7 @@
         </is>
       </c>
       <c r="E1498" t="n">
-        <v>69.95</v>
+        <v>65.95</v>
       </c>
       <c r="F1498" t="inlineStr">
         <is>
@@ -71072,7 +71074,7 @@
         </is>
       </c>
       <c r="E1499" t="n">
-        <v>88.5</v>
+        <v>75.95</v>
       </c>
       <c r="F1499" t="inlineStr">
         <is>
@@ -71119,7 +71121,7 @@
         </is>
       </c>
       <c r="E1500" t="n">
-        <v>60.5</v>
+        <v>55.95</v>
       </c>
       <c r="F1500" t="inlineStr">
         <is>
@@ -77824,7 +77826,7 @@
         </is>
       </c>
       <c r="E1643" t="n">
-        <v>658.5</v>
+        <v>584.95</v>
       </c>
       <c r="F1643" t="inlineStr">
         <is>
@@ -78566,7 +78568,7 @@
         </is>
       </c>
       <c r="E1659" t="n">
-        <v>1380.7</v>
+        <v>1249.95</v>
       </c>
       <c r="F1659" t="inlineStr">
         <is>
@@ -79446,7 +79448,7 @@
         </is>
       </c>
       <c r="E1677" t="n">
-        <v>28.5</v>
+        <v>26.95</v>
       </c>
       <c r="F1677" t="inlineStr">
         <is>
@@ -79493,7 +79495,7 @@
         </is>
       </c>
       <c r="E1678" t="n">
-        <v>31.5</v>
+        <v>29.5</v>
       </c>
       <c r="F1678" t="inlineStr">
         <is>
@@ -79540,7 +79542,7 @@
         </is>
       </c>
       <c r="E1679" t="n">
-        <v>51.5</v>
+        <v>48.5</v>
       </c>
       <c r="F1679" t="inlineStr">
         <is>
@@ -79587,7 +79589,7 @@
         </is>
       </c>
       <c r="E1680" t="n">
-        <v>37.5</v>
+        <v>35.5</v>
       </c>
       <c r="F1680" t="inlineStr">
         <is>
@@ -79634,7 +79636,7 @@
         </is>
       </c>
       <c r="E1681" t="n">
-        <v>58.95</v>
+        <v>55.5</v>
       </c>
       <c r="F1681" t="inlineStr">
         <is>
@@ -79681,7 +79683,7 @@
         </is>
       </c>
       <c r="E1682" t="n">
-        <v>68.95</v>
+        <v>63.95</v>
       </c>
       <c r="F1682" t="inlineStr">
         <is>
@@ -79728,7 +79730,7 @@
         </is>
       </c>
       <c r="E1683" t="n">
-        <v>31.5</v>
+        <v>29.5</v>
       </c>
       <c r="F1683" t="inlineStr">
         <is>
@@ -80151,7 +80153,7 @@
         </is>
       </c>
       <c r="E1692" t="n">
-        <v>80.95</v>
+        <v>69.95</v>
       </c>
       <c r="F1692" t="inlineStr">
         <is>
@@ -84432,7 +84434,7 @@
         </is>
       </c>
       <c r="E1783" t="n">
-        <v>45.95</v>
+        <v>41.5</v>
       </c>
       <c r="F1783" t="inlineStr">
         <is>
@@ -84949,7 +84951,7 @@
         </is>
       </c>
       <c r="E1794" t="n">
-        <v>73.5</v>
+        <v>75.95</v>
       </c>
       <c r="F1794" t="inlineStr">
         <is>
@@ -84996,7 +84998,7 @@
         </is>
       </c>
       <c r="E1795" t="n">
-        <v>73.5</v>
+        <v>75.95</v>
       </c>
       <c r="F1795" t="inlineStr">
         <is>
@@ -85043,7 +85045,7 @@
         </is>
       </c>
       <c r="E1796" t="n">
-        <v>73.5</v>
+        <v>75.95</v>
       </c>
       <c r="F1796" t="inlineStr">
         <is>
@@ -86171,7 +86173,7 @@
         </is>
       </c>
       <c r="E1820" t="n">
-        <v>63.5</v>
+        <v>69.95</v>
       </c>
       <c r="F1820" t="inlineStr">
         <is>
@@ -88296,7 +88298,7 @@
         </is>
       </c>
       <c r="E1865" t="n">
-        <v>55.95</v>
+        <v>59.95</v>
       </c>
       <c r="F1865" t="inlineStr">
         <is>
@@ -88919,7 +88921,7 @@
         </is>
       </c>
       <c r="E1878" t="n">
-        <v>47.95</v>
+        <v>51.5</v>
       </c>
       <c r="F1878" t="inlineStr">
         <is>
@@ -89452,7 +89454,7 @@
         </is>
       </c>
       <c r="E1889" t="n">
-        <v>66.95</v>
+        <v>79.95</v>
       </c>
       <c r="F1889" t="inlineStr">
         <is>
@@ -93581,7 +93583,9 @@
           <t>4 OZ</t>
         </is>
       </c>
-      <c r="E1983" t="inlineStr"/>
+      <c r="E1983" t="n">
+        <v>27.5</v>
+      </c>
       <c r="F1983" t="inlineStr">
         <is>
           <t>GOYA PLANTAIN CHIPS ADOBO FLVR</t>
@@ -93626,7 +93630,9 @@
           <t>7 OZ</t>
         </is>
       </c>
-      <c r="E1984" t="inlineStr"/>
+      <c r="E1984" t="n">
+        <v>22.5</v>
+      </c>
       <c r="F1984" t="inlineStr">
         <is>
           <t>GOYA TOSTONES ADOBO FLVR</t>
